--- a/experiment/HAT_2CH_bestx4/Test/results-Manga109/Manga109.xlsx
+++ b/experiment/HAT_2CH_bestx4/Test/results-Manga109/Manga109.xlsx
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.02</v>
+        <v>31.01</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8138</v>
+        <v>0.8137</v>
       </c>
     </row>
     <row r="4">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.33</v>
+        <v>28.32</v>
       </c>
       <c r="C4" t="n">
         <v>0.8468</v>
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.9</v>
+        <v>35.87</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9475</v>
+        <v>0.9474</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39.95</v>
+        <v>39.92</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9795</v>
+        <v>0.9791</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.11</v>
+        <v>30.09</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9156</v>
+        <v>0.9155</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.33</v>
+        <v>33.28</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9576</v>
+        <v>0.9575</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.28</v>
+        <v>27.29</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8952</v>
+        <v>0.8955</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.89</v>
+        <v>30.85</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9296</v>
+        <v>0.9293</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         <v>29.63</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8976</v>
+        <v>0.8979</v>
       </c>
     </row>
     <row r="12">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29.33</v>
+        <v>29.22</v>
       </c>
       <c r="C12" t="n">
         <v>0.95</v>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.17</v>
+        <v>28.16</v>
       </c>
       <c r="C13" t="n">
         <v>0.8658</v>
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33.62</v>
+        <v>33.67</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9619</v>
+        <v>0.9625</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.14</v>
+        <v>32.13</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9034</v>
+        <v>0.9035</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.72</v>
+        <v>28.78</v>
       </c>
       <c r="C16" t="n">
-        <v>0.918</v>
+        <v>0.9183</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.79</v>
+        <v>27.8</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9097</v>
+        <v>0.9095</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.14</v>
+        <v>31.08</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9578</v>
+        <v>0.9574</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30.85</v>
+        <v>30.84</v>
       </c>
       <c r="C20" t="n">
         <v>0.902</v>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32.94</v>
+        <v>32.9</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9765</v>
+        <v>0.9764</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.05</v>
+        <v>32.09</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9233</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.13</v>
+        <v>32.06</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9351</v>
+        <v>0.9344</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.29</v>
+        <v>30.28</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.9136</v>
       </c>
     </row>
     <row r="25">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>37.3</v>
+        <v>37.29</v>
       </c>
       <c r="C25" t="n">
         <v>0.972</v>
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.07</v>
+        <v>29.05</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9571</v>
       </c>
     </row>
     <row r="27">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.09</v>
+        <v>31.07</v>
       </c>
       <c r="C27" t="n">
         <v>0.9402</v>
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38.42</v>
+        <v>38.44</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9781</v>
+        <v>0.9782999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.56</v>
+        <v>31.5</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9323</v>
+        <v>0.9319</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>33.37</v>
+        <v>33.38</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9595</v>
+        <v>0.9596</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.48</v>
+        <v>31.49</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9431</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26.87</v>
+        <v>26.83</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9405</v>
+        <v>0.9404</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27.83</v>
+        <v>27.8</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9323</v>
+        <v>0.9324</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.63</v>
+        <v>32.61</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8951</v>
+        <v>0.8953</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>28.65</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7448</v>
+        <v>0.7451</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26.49</v>
+        <v>26.48</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8721</v>
+        <v>0.8719</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.57</v>
+        <v>31.56</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9122</v>
+        <v>0.9123</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.72</v>
+        <v>27.73</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8648</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35.34</v>
+        <v>35.39</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9714</v>
+        <v>0.9716</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>34.91</v>
+        <v>34.89</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9627</v>
+        <v>0.9626</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28.28</v>
+        <v>28.3</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9006</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30.73</v>
+        <v>30.8</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8661</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32.64</v>
+        <v>32.6</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9147</v>
+        <v>0.9144</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20.92</v>
+        <v>20.91</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7478</v>
       </c>
     </row>
     <row r="45">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>35.29</v>
+        <v>35.31</v>
       </c>
       <c r="C45" t="n">
         <v>0.9777</v>
@@ -1027,7 +1027,7 @@
         <v>25.13</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9191</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="47">
@@ -1040,7 +1040,7 @@
         <v>27.68</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9001</v>
+        <v>0.9003</v>
       </c>
     </row>
     <row r="48">
@@ -1053,7 +1053,7 @@
         <v>34.74</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9538</v>
+        <v>0.9536</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         <v>26.97</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8698</v>
+        <v>0.8701</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.76</v>
+        <v>28.77</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9182</v>
+        <v>0.9183</v>
       </c>
     </row>
     <row r="51">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26.72</v>
+        <v>26.71</v>
       </c>
       <c r="C51" t="n">
         <v>0.7625999999999999</v>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30.48</v>
+        <v>30.42</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9475</v>
+        <v>0.9472</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>33.36</v>
+        <v>33.32</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9459</v>
       </c>
     </row>
     <row r="54">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>36.38</v>
+        <v>36.39</v>
       </c>
       <c r="C54" t="n">
         <v>0.9044</v>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>35.76</v>
+        <v>35.78</v>
       </c>
       <c r="C55" t="n">
-        <v>0.964</v>
+        <v>0.9641</v>
       </c>
     </row>
     <row r="56">
@@ -1157,7 +1157,7 @@
         <v>22.64</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.7257</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>33.08</v>
+        <v>33</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9667</v>
+        <v>0.9663</v>
       </c>
     </row>
     <row r="58">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.48</v>
+        <v>31.38</v>
       </c>
       <c r="C58" t="n">
         <v>0.9484</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.87</v>
+        <v>31.84</v>
       </c>
       <c r="C59" t="n">
-        <v>0.945</v>
+        <v>0.9452</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>23.72</v>
+        <v>23.75</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7633</v>
+        <v>0.7641</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>33.62</v>
+        <v>33.59</v>
       </c>
       <c r="C61" t="n">
-        <v>0.971</v>
+        <v>0.9709</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9482</v>
+        <v>0.9481000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>30.96</v>
+        <v>30.97</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9504</v>
+        <v>0.9507</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35.01</v>
+        <v>35</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9678</v>
+        <v>0.9679</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         <v>34.02</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9274</v>
+        <v>0.9273</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.32</v>
+        <v>25.36</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9328</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>32.35</v>
+        <v>32.29</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9416</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>33.07</v>
+        <v>33.09</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9323</v>
+        <v>0.9324</v>
       </c>
     </row>
     <row r="69">
@@ -1326,7 +1326,7 @@
         <v>31.59</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9412</v>
       </c>
     </row>
     <row r="70">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>31.11</v>
+        <v>31.1</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9389</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -1365,7 +1365,7 @@
         <v>27.86</v>
       </c>
       <c r="C72" t="n">
-        <v>0.7114</v>
+        <v>0.7116</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>34.91</v>
+        <v>34.93</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9583</v>
+        <v>0.9585</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>33.99</v>
+        <v>34</v>
       </c>
       <c r="C74" t="n">
-        <v>0.9518</v>
+        <v>0.9519</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>28.3</v>
+        <v>28.31</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8923</v>
+        <v>0.8925</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>29.69</v>
+        <v>29.68</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9018</v>
+        <v>0.9016999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.37</v>
+        <v>30.4</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9314</v>
+        <v>0.9316</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>30.25</v>
+        <v>30.24</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8806</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         <v>28.09</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8102</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>31.09</v>
+        <v>31.08</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9351</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>31.01</v>
+        <v>30.99</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9407</v>
+        <v>0.9406</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>29.91</v>
+        <v>29.89</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8746</v>
+        <v>0.8744</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>31.9</v>
+        <v>31.92</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9038</v>
+        <v>0.9036999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>31.54</v>
+        <v>31.47</v>
       </c>
       <c r="C84" t="n">
         <v>0.96</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>27.72</v>
+        <v>27.69</v>
       </c>
       <c r="C85" t="n">
-        <v>0.945</v>
+        <v>0.9449</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>32.41</v>
+        <v>32.4</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9324</v>
+        <v>0.9326</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>28.5</v>
+        <v>28.52</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8754</v>
+        <v>0.8758</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35.69</v>
+        <v>35.71</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9532</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>33.91</v>
+        <v>33.85</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9629</v>
+        <v>0.9627</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>30.38</v>
+        <v>30.39</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9234</v>
+        <v>0.9236</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.39</v>
+        <v>25.42</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8631</v>
+        <v>0.8636</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>28.72</v>
+        <v>28.73</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.9127</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>27.41</v>
+        <v>27.38</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9494</v>
+        <v>0.9493</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>21.01</v>
+        <v>21.02</v>
       </c>
       <c r="C94" t="n">
-        <v>0.7386</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>34.29</v>
+        <v>34.25</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9549</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.68</v>
+        <v>26.65</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8835</v>
+        <v>0.8837</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>29.79</v>
+        <v>29.78</v>
       </c>
       <c r="C97" t="n">
-        <v>0.9083</v>
+        <v>0.9085</v>
       </c>
     </row>
     <row r="98">
@@ -1703,7 +1703,7 @@
         <v>32.65</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8774</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>29.04</v>
+        <v>29.08</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9656</v>
+        <v>0.9659</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.83</v>
+        <v>25.82</v>
       </c>
       <c r="C100" t="n">
-        <v>0.759</v>
+        <v>0.7588</v>
       </c>
     </row>
     <row r="101">
@@ -1742,7 +1742,7 @@
         <v>23.68</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8933</v>
+        <v>0.8935999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.32</v>
+        <v>27.31</v>
       </c>
       <c r="C102" t="n">
-        <v>0.9033</v>
+        <v>0.9034</v>
       </c>
     </row>
     <row r="103">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>23.32</v>
+        <v>23.31</v>
       </c>
       <c r="C103" t="n">
-        <v>0.8303</v>
+        <v>0.8302</v>
       </c>
     </row>
     <row r="104">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>36.81</v>
+        <v>36.77</v>
       </c>
       <c r="C104" t="n">
-        <v>0.9761</v>
+        <v>0.9758</v>
       </c>
     </row>
     <row r="105">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>28.86</v>
+        <v>28.85</v>
       </c>
       <c r="C105" t="n">
-        <v>0.909</v>
+        <v>0.9088000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>33.9</v>
+        <v>33.88</v>
       </c>
       <c r="C106" t="n">
         <v>0.9774</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>29.56</v>
+        <v>29.55</v>
       </c>
       <c r="C107" t="n">
         <v>0.8875</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>36.57</v>
+        <v>36.42</v>
       </c>
       <c r="C108" t="n">
-        <v>0.9381</v>
+        <v>0.9377</v>
       </c>
     </row>
     <row r="109">
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>28.33</v>
+        <v>28.34</v>
       </c>
       <c r="C110" t="n">
-        <v>0.9084</v>
+        <v>0.9083</v>
       </c>
     </row>
     <row r="111">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>30.6</v>
+        <v>30.59</v>
       </c>
       <c r="C111" t="n">
         <v>0.9104</v>
